--- a/脚本/3.0.5/运营/综合信披/ORACLE/3期性能优化/中债三期优化代码清单.xlsx
+++ b/脚本/3.0.5/运营/综合信披/ORACLE/3期性能优化/中债三期优化代码清单.xlsx
@@ -1,21 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25128"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E695730C-FA59-4DEB-AB73-FD696ECEB6DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10425"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CHB_SUBMIT_STATUS改造" sheetId="1" r:id="rId1"/>
-    <sheet name="三期优化" sheetId="2" r:id="rId2"/>
+    <sheet name="其余三期优化" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>background-component/msg-generate/src/main/java/com/joyintech/component/svrreport/chb/dto/ChbSubmitStatusDto.java</t>
   </si>
@@ -110,133 +121,138 @@
     <t>tams-svreport-parent/tams-svreport/src/main/resources/templates/report/system/debtsubmitinfo/DebtSubmitInfo002.html</t>
   </si>
   <si>
+    <t>tams-svreport-parent/tams-svreport-chb3/src/main/java/com/joyintech/tams/report/submitmanagement/investorsholdinforegist/controller/InvestorsHoldInfoRegist001Controller.java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tams-svreport-parent/tams-svreport-chb3/src/main/resources/templates/report/submitmanagement/investorsholdinforegist/InvestorsHoldInfoRegist001.html</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tams-common/src/main/java/com/joyintech/tams/common/base/dao/ChbEquTmpMapper.java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tams-common/src/main/java/com/joyintech/tams/common/base/dao/sqlmap/ChbEquTmpMapper.xml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tams-common/src/main/java/com/joyintech/tams/common/base/entity/ChbEquTmp.java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/investormerger/dao/ChbEquHoldCheckDtoMapper.java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/investormerger/dao/sqlmap/ChbEquHoldCheckDtoMapper.xml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/investormerger/dto/ChbEquHoldCheckDto.java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/submitmaintenance/equityinfo/dao/EquityInfoDistinctMapper.java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/submitmaintenance/equityinfo/dao/sqlmap/EquityInfoDistinctMapper.xml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/submitmaintenance/investorsholdinfo/dao/sqlmap/InvestorsHoldInfo001Mapper.xml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/submitmaintenance/investorsholdinfo/service/InvestorsHoldInfo001Service.java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/submitmaintenance/investorsholdinfo/service/InvestorsHoldInfoDistinctService.java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tams-svreport-batch/tams-svreport-batch-chb3/src/main/java/com/joyintech/tams/batch/report/autosendcb/cnbondupinterf/runner/CnBondUpInterfService.java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tams-svreport-batch/tams-svreport-batch-chb3/src/main/java/com/joyintech/tams/batch/report/autosendcb/cnbondupinterf/service/Chb3CnBondUpInterfTaskService.java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tams-svreport-common/src/main/java/com/joyintech/tams/report/interf/common/util/SftpUtil.java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/submitmaintenance/equityinfo/service/EquityInfo001Service.java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/submitmaintenance/equityinfo/service/EquityInfoDistinctService.java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/investormerger/dao/ChbInvestholdInfoCheckDtoMapper.java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/investormerger/dao/sqlmap/ChbInvestholdInfoCheckDtoMapper.xml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/submitmaintenance/investorsholdinfo/dao/InvestorsHoldInfo001Mapper.java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/investormerger/dto/ChbInvestholdInfoCheckDto.java</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tams-system/yunying/app/src/main/resources/application.yml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tams-system/yunying/batch/src/main/resources/application.yml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>脚本/3.0.5/运营/综合信披/3期性能优化/20220321_身份接入临时表.sql</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>脚本/3.0.5/运营/综合信披/3期性能优化/20220328_持有接入临时表.sql</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>脚本/3.0.5/运营/综合信披/3期性能优化/索引重建-根据需要执行/20220321_0000此文件为产品身份和持有表索引备份.sql</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>脚本/3.0.5/运营/综合信披/3期性能优化/索引重建-根据需要执行/20220321_三期持有者持有info和sub和check索引重建.sql</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>脚本/3.0.5/运营/综合信披/3期性能优化/索引重建-根据需要执行/20220321_三期持有者身份info和sub和check索引重建.sql</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>脚本/3.0.5/运营/综合信披/20220330_三期关于中债四期的参数配置默认不影响.sql</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>脚本/3.0.5/运营/综合信披/3期性能优化/20220309_CHBSUBMITSTATUS表删除相关改造.sql</t>
-  </si>
-  <si>
-    <t>tams-svreport-parent/tams-svreport-chb3/src/main/java/com/joyintech/tams/report/submitmanagement/investorsholdinforegist/controller/InvestorsHoldInfoRegist001Controller.java</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tams-svreport-parent/tams-svreport-chb3/src/main/resources/templates/report/submitmanagement/investorsholdinforegist/InvestorsHoldInfoRegist001.html</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tams-common/src/main/java/com/joyintech/tams/common/base/dao/ChbEquTmpMapper.java</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tams-common/src/main/java/com/joyintech/tams/common/base/dao/sqlmap/ChbEquTmpMapper.xml</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tams-common/src/main/java/com/joyintech/tams/common/base/entity/ChbEquTmp.java</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/investormerger/dao/ChbEquHoldCheckDtoMapper.java</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/investormerger/dao/sqlmap/ChbEquHoldCheckDtoMapper.xml</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/investormerger/dto/ChbEquHoldCheckDto.java</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/submitmaintenance/equityinfo/dao/EquityInfoDistinctMapper.java</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/submitmaintenance/equityinfo/dao/sqlmap/EquityInfoDistinctMapper.xml</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/submitmaintenance/investorsholdinfo/dao/sqlmap/InvestorsHoldInfo001Mapper.xml</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/submitmaintenance/investorsholdinfo/service/InvestorsHoldInfo001Service.java</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/submitmaintenance/investorsholdinfo/service/InvestorsHoldInfoDistinctService.java</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tams-svreport-batch/tams-svreport-batch-chb3/src/main/java/com/joyintech/tams/batch/report/autosendcb/cnbondupinterf/runner/CnBondUpInterfService.java</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tams-svreport-batch/tams-svreport-batch-chb3/src/main/java/com/joyintech/tams/batch/report/autosendcb/cnbondupinterf/service/Chb3CnBondUpInterfTaskService.java</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tams-svreport-common/src/main/java/com/joyintech/tams/report/interf/common/util/SftpUtil.java</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/submitmaintenance/equityinfo/service/EquityInfo001Service.java</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/submitmaintenance/equityinfo/service/EquityInfoDistinctService.java</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/investormerger/dao/ChbInvestholdInfoCheckDtoMapper.java</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/investormerger/dao/sqlmap/ChbInvestholdInfoCheckDtoMapper.xml</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/submitmaintenance/investorsholdinfo/dao/InvestorsHoldInfo001Mapper.java</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tams-svreport-parent/tams-svreport-busicom/src/main/java/com/joyintech/tams/report/investormerger/dto/ChbInvestholdInfoCheckDto.java</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tams-system/yunying/app/src/main/resources/application.yml</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>tams-system/yunying/batch/src/main/resources/application.yml</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>脚本/3.0.5/运营/综合信披/3期性能优化/20220321_身份接入临时表.sql</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>脚本/3.0.5/运营/综合信披/3期性能优化/20220328_持有接入临时表.sql</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>脚本/3.0.5/运营/综合信披/3期性能优化/索引重建-根据需要执行/20220321_0000此文件为产品身份和持有表索引备份.sql</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>脚本/3.0.5/运营/综合信披/3期性能优化/索引重建-根据需要执行/20220321_三期持有者持有info和sub和check索引重建.sql</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>脚本/3.0.5/运营/综合信披/3期性能优化/索引重建-根据需要执行/20220321_三期持有者身份info和sub和check索引重建.sql</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>脚本/3.0.5/运营/综合信披/20220330_三期关于中债四期的参数配置默认不影响.sql</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>脚本/3.0.5/运营/综合信披/3期性能优化/20220429_数据移植优化_删除CHB_SUBMIT_STATUS表所需的数据移植脚本</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -293,7 +309,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -368,6 +384,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -403,6 +436,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -578,168 +628,173 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:C32"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="C1:C33"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="1" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="2" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="3" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="4" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="5" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="6" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="7" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="8" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="9" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="10" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="11" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="12" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="13" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="14" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="15" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="16" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C17" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C20" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C21" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="22" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C22" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="23" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C23" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="24" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C24" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="25" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="26" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C26" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="27" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="28" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="29" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C29" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="30" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="31" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="32" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C32" t="s">
-        <v>31</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -750,158 +805,158 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A31"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A5" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A8" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A10" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A13" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A17" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A18" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A19" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A20" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A21" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A22" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A23" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A24" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A26" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A27" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A28" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A29" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A30" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A31" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>
